--- a/public/templates/vat-invoice-listing-01-1-gtgt.xlsx
+++ b/public/templates/vat-invoice-listing-01-1-gtgt.xlsx
@@ -1656,7 +1656,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="293">
+  <cellXfs count="294">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2529,6 +2529,9 @@
     </xf>
     <xf numFmtId="0" fontId="287" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3164,7 +3167,7 @@
       <c r="J16" s="256"/>
       <c r="K16" s="257"/>
     </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>1</v>
       </c>
@@ -3180,7 +3183,7 @@
       <c r="E17" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="293" t="s">
         <v>40</v>
       </c>
       <c r="G17" s="36" t="s">
